--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,14 +12676,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13264,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,29 +13348,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,29 +13412,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13552,17 +13552,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13680,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -13712,17 +13712,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,29 +13732,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13904,17 +13904,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
@@ -13936,17 +13936,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14091,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,7 +14123,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14160,17 +14160,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,29 +13348,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,29 +13412,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13520,17 +13520,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,29 +13668,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13739,22 +13739,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
@@ -13776,17 +13776,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
@@ -13904,17 +13904,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,29 +13956,29 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -14032,17 +14032,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -14064,17 +14064,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14084,29 +14084,29 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14155,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14192,17 +14192,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14288,17 +14288,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13008,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13328,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,14 +13668,14 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -13685,12 +13685,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -13904,17 +13904,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13936,17 +13936,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -14005,12 +14005,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -14128,17 +14128,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14155,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,7 +14219,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14256,17 +14256,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14288,17 +14288,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13264,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13328,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,29 +13412,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -13488,17 +13488,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -13685,12 +13685,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,29 +13732,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13860,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,29 +13956,29 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,14 +13988,14 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -14005,12 +14005,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14160,17 +14160,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14320,17 +14320,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
@@ -12907,22 +12907,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,29 +13412,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13488,17 +13488,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,29 +13668,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,29 +13732,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13808,17 +13808,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,29 +13828,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13877,12 +13877,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -14000,17 +14000,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14160,17 +14160,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -12779,22 +12779,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13008,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -13296,17 +13296,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13328,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13680,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13904,17 +13904,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14155,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14288,17 +14288,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -12917,12 +12917,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13456,17 +13456,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -13488,17 +13488,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13680,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13712,17 +13712,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,29 +13732,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,29 +13828,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13860,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -14096,17 +14096,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,14 +12740,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -12757,12 +12757,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13264,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13680,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,29 +13732,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13776,17 +13776,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13808,17 +13808,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,29 +13828,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -14000,17 +14000,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14155,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14192,17 +14192,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,7 +14251,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -14261,12 +14261,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,14 +13092,14 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,14 +13124,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
@@ -13296,17 +13296,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,14 +13348,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -13520,17 +13520,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,29 +13668,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13712,17 +13712,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,29 +13732,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13776,17 +13776,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -13808,17 +13808,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,14 +13828,14 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -13845,12 +13845,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13860,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,29 +13956,29 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -14032,17 +14032,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -14064,17 +14064,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14084,29 +14084,29 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,14 +12644,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13008,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -13365,12 +13365,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13476,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13552,17 +13552,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,29 +13668,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13776,17 +13776,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13808,17 +13808,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
@@ -13936,17 +13936,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,29 +13956,29 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -14000,17 +14000,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14187,7 +14187,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14251,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,14 +12996,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,29 +13220,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13296,17 +13296,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13328,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,29 +13348,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13488,17 +13488,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
@@ -13552,17 +13552,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13611,22 +13611,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13707,22 +13707,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,29 +13828,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13860,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13936,17 +13936,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13968,17 +13968,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14155,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
@@ -12597,12 +12597,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13008,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13316,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,29 +13348,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,29 +13412,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13488,17 +13488,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13680,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13796,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,29 +13828,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13860,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,29 +13892,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,29 +13924,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,29 +13956,29 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14091,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14187,22 +14187,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14219,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,7 +14251,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -14261,12 +14261,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14315,22 +14315,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14347,22 +14347,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14448,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11971,12 +11971,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,14 +12612,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13008,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13232,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,29 +13252,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13284,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13328,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13380,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,29 +13412,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13444,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
@@ -13520,17 +13520,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,29 +13540,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -13675,22 +13675,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,29 +13700,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13764,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13808,17 +13808,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13860,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
@@ -13904,17 +13904,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13963,22 +13963,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +13988,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -14123,22 +14123,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14155,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14256,17 +14256,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,7 +14283,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14320,17 +14320,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14352,17 +14352,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14416,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -14480,17 +14480,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8774</v>
+        <v>8776</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8734</v>
+        <v>8736</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-40</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,59 +6612,59 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D274" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>-1</v>
+      <c r="C274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E275" s="3" t="n">
         <v>-1</v>
@@ -6696,59 +6696,59 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="E276" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+      <c r="A277" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="D277" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="E277" s="2" t="n">
-        <v>0</v>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+      <c r="A278" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D278" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E278" s="2" t="n">
-        <v>0</v>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="279">
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E299" s="2" t="n">
         <v>0</v>
@@ -7200,59 +7200,59 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C300" s="2" t="n">
+      <c r="C302" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D300" s="2" t="n">
+      <c r="D302" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E300" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D301" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E301" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C302" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D302" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E302" s="4" t="n">
-        <v>1</v>
+      <c r="E302" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -7263,59 +7263,59 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C303" s="4" t="n">
+      <c r="C305" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D303" s="4" t="n">
+      <c r="D305" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E303" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D304" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E304" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D305" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E305" s="2" t="n">
-        <v>0</v>
+      <c r="E305" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0</v>
@@ -7930,19 +7930,19 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E335" s="2" t="n">
         <v>0</v>
@@ -7951,19 +7951,19 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E336" s="2" t="n">
         <v>0</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E337" s="2" t="n">
         <v>0</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
@@ -8523,14 +8523,14 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D364" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E364" s="2" t="n">
         <v>0</v>
@@ -8560,19 +8560,19 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E365" s="2" t="n">
         <v>0</v>
@@ -8581,19 +8581,19 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C366" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E366" s="2" t="n">
         <v>0</v>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
@@ -8691,14 +8691,14 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E373" s="2" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -8791,19 +8791,19 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D400" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E400" s="2" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D403" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E403" s="2" t="n">
         <v>0</v>
@@ -9384,59 +9384,59 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C404" s="2" t="n">
+      <c r="C406" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D404" s="2" t="n">
+      <c r="D406" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E404" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="3" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C405" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="D405" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="E405" s="3" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B406" s="3" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C406" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="D406" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="E406" s="3" t="n">
-        <v>-4</v>
+      <c r="E406" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C407" s="3" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="E407" s="3" t="n">
         <v>-4</v>
@@ -9468,17 +9468,17 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E408" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="409">
@@ -9489,17 +9489,17 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="E409" s="3" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="410">
@@ -9510,17 +9510,17 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="E410" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="411">
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>-2</v>
@@ -9552,17 +9552,17 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E412" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="413">
@@ -9573,17 +9573,17 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E413" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="414">
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>-1</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>-1</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>-1</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>-1</v>
@@ -9678,59 +9678,59 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="inlineStr">
+      <c r="A419" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B419" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C419" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="D419" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="E419" s="2" t="n">
-        <v>0</v>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D419" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E419" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="inlineStr">
+      <c r="A420" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B420" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C420" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D420" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E420" s="2" t="n">
-        <v>0</v>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D420" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E420" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="421">
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>0</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D431" s="2" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E431" s="2" t="n">
         <v>0</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>0</v>
@@ -10014,37 +10014,79 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D434" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E434" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C434" s="2" t="n">
+      <c r="C436" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D434" s="2" t="n">
+      <c r="D436" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E434" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="4" t="inlineStr">
+      <c r="E436" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B435" s="4" t="inlineStr">
+      <c r="B437" s="4" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C435" s="4" t="n">
+      <c r="C437" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="D435" s="4" t="n">
+      <c r="D437" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="E435" s="4" t="n">
+      <c r="E437" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11286,7 +11328,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11301,7 +11343,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11355,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11328,7 +11370,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12084,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12069,7 +12111,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12393,7 +12435,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12408,7 +12450,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12462,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12435,7 +12477,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12489,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12462,7 +12504,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12565,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12590,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12622,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,14 +12654,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12629,12 +12671,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12686,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12698,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12718,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12730,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12750,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12782,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12814,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12846,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12878,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12910,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12922,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12942,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12954,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12974,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12986,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +13006,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +13038,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13070,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13082,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13102,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13134,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13146,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13166,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13198,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13230,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -13227,22 +13269,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13252,7 +13294,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13306,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13284,29 +13326,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13316,29 +13358,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13348,7 +13390,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13360,17 +13402,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13380,29 +13422,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13412,7 +13454,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13424,17 +13466,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13444,29 +13486,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13476,29 +13518,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13508,7 +13550,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13520,17 +13562,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13540,7 +13582,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13552,17 +13594,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13614,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
@@ -13611,22 +13653,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13678,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13710,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13680,17 +13722,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13700,7 +13742,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13712,17 +13754,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13732,7 +13774,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13744,17 +13786,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13764,29 +13806,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13796,29 +13838,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13828,29 +13870,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13860,29 +13902,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13892,7 +13934,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13904,17 +13946,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13924,14 +13966,14 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -13941,12 +13983,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13956,29 +13998,29 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -13988,29 +14030,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14020,7 +14062,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -14091,22 +14133,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14123,7 +14165,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -14133,12 +14175,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14155,22 +14197,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14187,22 +14229,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14219,22 +14261,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14251,22 +14293,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14283,7 +14325,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -14293,12 +14335,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14320,17 +14362,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14352,17 +14394,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14416,17 +14458,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14436,7 +14478,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14448,17 +14490,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14468,7 +14510,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14480,17 +14522,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14500,7 +14542,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12570,17 +12570,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12590,29 +12590,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12634,17 +12634,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12654,29 +12654,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12698,17 +12698,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12730,17 +12730,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12750,29 +12750,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
@@ -12794,17 +12794,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12814,29 +12814,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -12890,17 +12890,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12910,29 +12910,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12942,29 +12942,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12974,29 +12974,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13006,29 +13006,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13038,29 +13038,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13082,17 +13082,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -13114,17 +13114,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13134,29 +13134,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13166,29 +13166,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13210,17 +13210,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13242,17 +13242,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13262,29 +13262,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13294,29 +13294,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13338,17 +13338,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13370,17 +13370,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
@@ -13402,17 +13402,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13422,29 +13422,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13454,29 +13454,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13486,29 +13486,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13518,14 +13518,14 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13594,17 +13594,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13614,29 +13614,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13646,29 +13646,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13678,29 +13678,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13710,29 +13710,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13742,29 +13742,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13774,29 +13774,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13838,29 +13838,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13870,29 +13870,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13902,29 +13902,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -13946,17 +13946,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13978,17 +13978,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -14010,17 +14010,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14030,29 +14030,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -14133,22 +14133,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14165,22 +14165,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14229,22 +14229,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14266,17 +14266,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14293,22 +14293,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14362,17 +14362,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14389,22 +14389,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14458,17 +14458,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14490,17 +14490,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14522,17 +14522,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
     </row>
@@ -12570,17 +12570,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12590,29 +12590,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12622,14 +12622,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12654,29 +12654,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12686,29 +12686,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -12757,22 +12757,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12794,17 +12794,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12814,29 +12814,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12846,29 +12846,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12878,29 +12878,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
@@ -12922,17 +12922,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -12954,17 +12954,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12974,29 +12974,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13006,29 +13006,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13038,29 +13038,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13070,29 +13070,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13102,29 +13102,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13146,17 +13146,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13166,14 +13166,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -13210,17 +13210,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -13242,17 +13242,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13262,29 +13262,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13306,17 +13306,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13370,17 +13370,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13390,29 +13390,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13422,29 +13422,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13454,29 +13454,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13486,29 +13486,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13530,17 +13530,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13562,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13594,17 +13594,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13626,17 +13626,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13646,29 +13646,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13678,29 +13678,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13722,17 +13722,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13742,29 +13742,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13774,29 +13774,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13818,17 +13818,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13838,29 +13838,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13882,17 +13882,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13902,29 +13902,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13934,29 +13934,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13966,29 +13966,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -14010,17 +14010,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14030,29 +14030,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
@@ -14133,22 +14133,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14170,17 +14170,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14197,22 +14197,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14229,22 +14229,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14266,17 +14266,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14293,22 +14293,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14325,22 +14325,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14357,22 +14357,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14389,22 +14389,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14458,17 +14458,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -14490,17 +14490,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14522,17 +14522,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（23家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（63家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（62条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（62家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（63条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -662,17 +662,17 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>865</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -854,14 +854,14 @@
         <v>1741</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8776</v>
+        <v>8777</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8736</v>
+        <v>8737</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-40</v>
@@ -4547,24 +4547,24 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D174" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>0</v>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="175">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>0</v>
@@ -4680,14 +4680,14 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>0</v>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>0</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>0</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>0</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>0</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -9699,38 +9699,38 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="3" t="inlineStr">
+      <c r="A420" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B420" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C420" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="D420" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E420" s="3" t="n">
-        <v>-1</v>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>205</v>
+        <v>35</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>205</v>
+        <v>35</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>0</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D431" s="2" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E431" s="2" t="n">
         <v>0</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>0</v>
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D434" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E434" s="2" t="n">
         <v>0</v>
@@ -10035,14 +10035,14 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D435" s="2" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="E435" s="2" t="n">
         <v>0</v>
@@ -10101,14 +10101,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10137,6 +10138,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10164,6 +10170,11 @@
           <t>天津市南开区黄河道 503 号</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10191,6 +10202,11 @@
           <t>新疆乌鲁木齐市米东区振兴南路289号</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10218,6 +10234,11 @@
           <t>重庆市两江新区经开园金渝大道99号16幢</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10245,6 +10266,11 @@
           <t>金玉路311号玉林万达广场1F1号门连廊</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10272,6 +10298,11 @@
           <t>桂林路66号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10299,6 +10330,11 @@
           <t>湖北省宜昌市宜都市陆城宜华大道102号宜都万达1F中庭</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10326,6 +10362,11 @@
           <t>湖北省武汉市武昌区和平大道659号滨江天街一层5号门中庭</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -10335,49 +10376,59 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小米汽车重庆万州区永佳路授权服务中心</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>永佳路343号</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆万州区永佳路授权服务中心</t>
+          <t>小鹏汽车成都武侯大道销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>永佳路343号</t>
+          <t>四川省成都市武侯区武兴路110号</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10389,22 +10440,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车成都武侯大道销售服务中心</t>
+          <t>小鹏汽车天津庞大汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区武兴路110号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10416,22 +10472,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车天津庞大汽车园销售服务中心</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>六安市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅</t>
+          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10443,22 +10504,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>小鹏汽车南通海安迎宾路汽车城销售展厅</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>六安市</t>
+          <t>南通市</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米</t>
+          <t>江苏省南通市海安市城东镇开发区迎宾路16号</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10470,22 +10536,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车南通海安迎宾路汽车城销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>南通市</t>
+          <t>抚州市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>江苏省南通市海安市城东镇开发区迎宾路16号</t>
+          <t>抚州市临川区临川大道小鹏服务中心</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10497,22 +10568,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>抚州市</t>
+          <t>许昌市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10524,22 +10600,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车贵阳新添大道销售展厅</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>许昌市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南</t>
+          <t>贵州省贵阳市乌当区新添大道64号B栋第一层门面</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10551,49 +10632,59 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳新添大道销售展厅</t>
+          <t>小鹏汽车西安量子晨销售展厅</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>贵州省贵阳市乌当区新添大道64号B栋第一层门面</t>
+          <t>雁塔区西影路466号</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车西安量子晨销售展厅</t>
+          <t>潍坊谷德广场</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>潍坊市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>雁塔区西影路466号</t>
+          <t>山东省潍坊市奎文区福寿东街4369号</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10605,22 +10696,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>潍坊谷德广场</t>
+          <t>福州苏宁广场</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>潍坊市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区福寿东街4369号</t>
+          <t>福建省福州市台江区工业路233号福州苏宁广场B座L1入口处</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10632,49 +10728,59 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>福州苏宁广场</t>
+          <t>西安龙首印象城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市台江区工业路233号福州苏宁广场B座L1入口处</t>
+          <t>陕西省西安市未央区未央路33号龙首印象城PA-L1-04</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>西安龙首印象城</t>
+          <t>AITO授权用户中心•北京亚市</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路33号龙首印象城PA-L1-04</t>
+          <t>北京市昌平区立汤路辅路与回南北路交叉口东北300米问界汽车</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10686,22 +10792,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•北京亚市</t>
+          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>北京市昌平区立汤路辅路与回南北路交叉口东北300米问界汽车</t>
+          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10713,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
+          <t>鸿蒙智行智界用户中心•江门冈州大道</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10723,39 +10834,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>东莞市</t>
+          <t>江门市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•江门冈州大道</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>江门市</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
           <t>广东省江门市新会区会城冈州大道东45号1座</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10778,6 +10867,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10806,6 +10896,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -10833,6 +10928,11 @@
           <t>荔湾区龙溪大道293号场地</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -10860,6 +10960,11 @@
           <t>广东省东莞市虎门镇太安路虎门段253号</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -10887,6 +10992,11 @@
           <t>广东省茂名市电白区坡心镇谭莲工业区高水路东侧</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -10914,6 +11024,11 @@
           <t>广东省韶关市浈江区韶南大道7公里</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -10941,6 +11056,11 @@
           <t>河南省新乡市延津县金穗大道东段京珠高速东2000米路北东安汽车园</t>
         </is>
       </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -10968,6 +11088,11 @@
           <t>厦门市湖里区港兴二路57号</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -10995,6 +11120,11 @@
           <t>山东省淄博市淄川区双杨镇十里村西</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11022,6 +11152,11 @@
           <t>陕西省西安市沣东新城丰产路56号</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -11049,6 +11184,11 @@
           <t>沙河万达一层中庭</t>
         </is>
       </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -11076,6 +11216,11 @@
           <t>吉林省长春市万达茂</t>
         </is>
       </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -11103,6 +11248,11 @@
           <t>广州大道北 1419 号 佳润广场</t>
         </is>
       </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -11130,6 +11280,11 @@
           <t>景兰路与文棠路交叉口北160米六合龙湖天街中庭</t>
         </is>
       </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -11157,6 +11312,11 @@
           <t>江苏省苏州市张家港吾悦商场一楼1号门</t>
         </is>
       </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 3 期</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -11184,6 +11344,11 @@
           <t>玉清路一号一层中庭</t>
         </is>
       </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -11211,6 +11376,11 @@
           <t>济源大道济源东方国际公馆东南侧宝龙广场1号门</t>
         </is>
       </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -11238,6 +11408,11 @@
           <t>神农万达广场2号门</t>
         </is>
       </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -11265,6 +11440,11 @@
           <t>广州市海珠区新滘西路68号小鹏汽车广州海珠销售服务中心</t>
         </is>
       </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -11292,6 +11472,11 @@
           <t>河南省郑州市中原区桐柏路与棉纺路交叉口锦艺城C区1号楼1-15号</t>
         </is>
       </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -11319,6 +11504,11 @@
           <t>湖北省十堰市张湾区万达广场1B层小鹏汽车</t>
         </is>
       </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -11328,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11343,7 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11370,7 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11397,7 +11597,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11424,7 +11629,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11454,6 +11664,11 @@
           <t>北京市大兴区北京市大兴区欣宁街15号</t>
         </is>
       </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -11481,6 +11696,11 @@
           <t>山东省淄博市世纪路昌国路交汇处东南角</t>
         </is>
       </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -11508,6 +11728,11 @@
           <t>潍坊市寒亭区通亭街2882号</t>
         </is>
       </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -11535,6 +11760,11 @@
           <t>广东省东莞市南城街道莞太路南城段454号</t>
         </is>
       </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -11562,6 +11792,11 @@
           <t>江苏省南通市崇川区桃园路2号</t>
         </is>
       </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -11589,6 +11824,11 @@
           <t>青海省西宁市城东区南山东路84号</t>
         </is>
       </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -11616,6 +11856,11 @@
           <t>广东省深圳市南山区西丽街道沙河西路丰泽园仓储中心三栋一层</t>
         </is>
       </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -11643,6 +11888,11 @@
           <t>浙江省台州市路桥区银座街508号负一层</t>
         </is>
       </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -11670,6 +11920,11 @@
           <t>湖北省武汉市江岸区新天地南馆一楼华为门口</t>
         </is>
       </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -11697,6 +11952,11 @@
           <t>西藏自治区拉萨市城关区纳金东路与红旗东路交叉口东南480米YX-HD-ZT-002</t>
         </is>
       </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -11724,6 +11984,11 @@
           <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -11751,6 +12016,11 @@
           <t>成都市新都区三河街道五龙山路127号</t>
         </is>
       </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -11778,6 +12048,11 @@
           <t>四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -11805,6 +12080,11 @@
           <t>山东省济南市历城区将军路1688号华山环宇城1楼</t>
         </is>
       </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -11832,6 +12112,11 @@
           <t>山东省淄博市张店区金晶大道66号万象汇一楼2号门入口处</t>
         </is>
       </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -11859,6 +12144,11 @@
           <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
         </is>
       </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -11886,6 +12176,11 @@
           <t>山东省菏泽市定陶区杜堂镇迎旭路与曙光路交叉口北200米</t>
         </is>
       </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -11913,6 +12208,11 @@
           <t>广东省中山市火炬开发区江陵西路36号之三</t>
         </is>
       </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -11940,6 +12240,11 @@
           <t>广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城D1号展场</t>
         </is>
       </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -11967,6 +12272,11 @@
           <t>江苏省常州市金坛区金坛汽车城9号</t>
         </is>
       </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -11994,6 +12304,11 @@
           <t>江苏省无锡市锡山区安镇街道先锋中路25-4号</t>
         </is>
       </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -12021,6 +12336,11 @@
           <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -12048,6 +12368,11 @@
           <t>江西省抚州市临川区万达广场1036号</t>
         </is>
       </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -12075,6 +12400,11 @@
           <t>浙江省嘉兴市嘉善县罗星街道银泰百货399号1楼华为店L1-102-2</t>
         </is>
       </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -12084,7 +12414,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>AITO授权用户中心•宁波下应</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12100,6 +12430,11 @@
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>浙江省宁波市鄞州区下应北路800号</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12127,6 +12462,11 @@
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>浙江省宁波市鄞州区下应北路800号</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12156,6 +12496,11 @@
           <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼1层03号</t>
         </is>
       </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -12183,6 +12528,11 @@
           <t>湖北省武汉市黄陂区滠口街道滠口村刘店村汉口北汽车大世界W1号H-2#A号-1</t>
         </is>
       </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -12210,6 +12560,11 @@
           <t>湖南省怀化市鹤城区城南街道怀化国际汽车城内原丰田4S店</t>
         </is>
       </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -12237,6 +12592,11 @@
           <t>福建省福州市仓山区盖山镇齐安路767号7号楼3单元</t>
         </is>
       </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -12246,7 +12606,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12261,7 +12621,12 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12638,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12288,7 +12653,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12318,6 +12688,11 @@
           <t>辽宁省大连市甘井子区虹韵路6号万达广场1A层1A51号</t>
         </is>
       </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -12345,6 +12720,11 @@
           <t>辽宁省沈阳市浑南区创新二路37-1号</t>
         </is>
       </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -12354,22 +12734,27 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>鸿蒙智行授权用户中心•延安宝塔汽车园</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>延安市</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2</t>
+          <t>陕西省延安市宝塔区李渠镇杨兴庄汽车城4号</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12381,22 +12766,27 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•延安宝塔汽车园</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>延安市</t>
+          <t>西宁市</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>陕西省延安市宝塔区李渠镇杨兴庄汽车城4号</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12798,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12423,7 +12813,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12453,6 +12848,11 @@
           <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -12480,31 +12880,9 @@
           <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>西宁市</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12519,13 +12897,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
@@ -12570,17 +12948,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12590,7 +12968,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12602,17 +12980,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12622,7 +13000,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
@@ -12634,17 +13012,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12654,29 +13032,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12686,7 +13064,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12698,17 +13076,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12718,7 +13096,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12735,12 +13113,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12750,29 +13128,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12782,29 +13160,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12814,29 +13192,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12846,29 +13224,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12878,7 +13256,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
@@ -12890,17 +13268,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12910,29 +13288,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12942,7 +13320,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12954,17 +13332,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12974,7 +13352,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12986,17 +13364,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13006,7 +13384,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13401,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13038,29 +13416,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13070,29 +13448,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13102,7 +13480,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
@@ -13114,17 +13492,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13134,29 +13512,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13166,7 +13544,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
@@ -13178,17 +13556,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13198,7 +13576,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13210,17 +13588,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13230,7 +13608,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
@@ -13269,22 +13647,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13294,7 +13672,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
@@ -13306,17 +13684,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13326,29 +13704,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13358,29 +13736,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13390,29 +13768,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13422,7 +13800,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -13466,17 +13844,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13486,29 +13864,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13518,7 +13896,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -13530,17 +13908,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13550,7 +13928,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13940,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13582,29 +13960,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13614,7 +13992,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13626,17 +14004,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13646,29 +14024,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13678,29 +14056,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13710,29 +14088,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13742,29 +14120,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13774,7 +14152,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13818,17 +14196,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13838,29 +14216,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13870,29 +14248,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13902,29 +14280,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -13934,29 +14312,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13966,7 +14344,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
@@ -13978,17 +14356,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -13998,7 +14376,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -14010,17 +14388,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14030,29 +14408,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14062,39 +14440,39 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
@@ -14133,54 +14511,54 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14202,17 +14580,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>AITO授权用户中心•都匀茂盛汽车城</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14266,17 +14644,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14293,22 +14671,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14325,22 +14703,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14357,22 +14735,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14394,17 +14772,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14421,22 +14799,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>沈阳铁西万象汇城市展厅一号门</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>沈阳铁西万象汇体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -14446,39 +14824,39 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 63%</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>沈阳铁西万象汇城市展厅一号门</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>沈阳铁西万象汇体验店</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>地址相似度 63%</t>
         </is>
       </c>
     </row>
@@ -14543,6 +14921,38 @@
       <c r="F63" s="5" t="inlineStr">
         <is>
           <t>店名相似度 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>华为智能生活馆•蚌埠银泰</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>华为智能生活馆•蚌埠银泰城</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>店名变更</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -10867,7 +10867,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「东营市奥润汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「淄博宝通汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「太原顺宝行汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车广州黄埔销售服务中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「鸿蒙智行授权用户中心•成都五龙山」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「AITO授权用户中心•中山江陵西路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>连续在档 1 期</t>
+          <t>连续在档 1 期；本期存在高相似店名「鸿蒙智行授权用户中心•无锡先锋中路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12328,12 +12328,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期存在高相似店名「鸿蒙智行授权用户中心•宁波下应」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「鸿蒙智行授权用户中心•怀化国际汽车城」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期存在高相似店名「鸿蒙智行尚界用户中心•沈阳创新二路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「AITO授权用户中心•延安宝塔汽车园」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区南川工业园区同安路182号</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「鸿蒙智行授权用户中心•西宁同安路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13352,29 +13352,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13384,29 +13384,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
+          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13556,17 +13556,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
         </is>
       </c>
     </row>
@@ -13588,17 +13588,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13608,29 +13608,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
+          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13640,29 +13640,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13672,29 +13672,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13704,29 +13704,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13748,17 +13748,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13780,17 +13780,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13800,29 +13800,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13832,29 +13832,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13876,17 +13876,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -13908,17 +13908,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
         </is>
       </c>
     </row>
@@ -13940,17 +13940,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13972,17 +13972,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -14004,17 +14004,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -14036,17 +14036,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14056,29 +14056,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14088,29 +14088,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14120,29 +14120,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14152,29 +14152,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>鸿蒙智行智界用户中心•郑州西四环</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
         </is>
       </c>
     </row>
@@ -14196,17 +14196,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
         </is>
       </c>
     </row>
@@ -14228,17 +14228,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14248,29 +14248,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
+          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
         </is>
       </c>
     </row>
@@ -14292,17 +14292,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
+          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
         </is>
       </c>
     </row>
@@ -14324,17 +14324,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>鸿蒙智行授权用户中心•大连香周路</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14344,29 +14344,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -14388,17 +14388,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14408,29 +14408,29 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14440,29 +14440,29 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -14484,17 +14484,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -14516,17 +14516,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -14607,22 +14607,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14676,17 +14676,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水通源</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14708,17 +14708,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14767,22 +14767,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -14799,22 +14799,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>AITO授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（62家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（63条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1741</v>
+        <v>1473</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1715</v>
+        <v>1458</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-26</v>
+        <v>-15</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.0%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8777</v>
+        <v>8509</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8737</v>
+        <v>8480</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-40</v>
+        <v>-29</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C407" s="3" t="n">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="E407" s="3" t="n">
         <v>-4</v>
@@ -9468,17 +9468,17 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>155</v>
+        <v>9</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>151</v>
+        <v>6</v>
       </c>
       <c r="E408" s="3" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="409">
@@ -9489,17 +9489,17 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="E409" s="3" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="410">
@@ -9514,13 +9514,13 @@
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E410" s="3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="411">
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>-2</v>
@@ -9552,17 +9552,17 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E412" s="3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="413">
@@ -9573,17 +9573,17 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E413" s="3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="414">
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>-1</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>-1</v>
@@ -9636,80 +9636,80 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="inlineStr">
+      <c r="A417" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B417" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C417" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="D417" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="E417" s="3" t="n">
-        <v>-1</v>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="3" t="inlineStr">
+      <c r="A418" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B418" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C418" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="D418" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="E418" s="3" t="n">
-        <v>-1</v>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="3" t="inlineStr">
+      <c r="A419" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B419" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C419" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="D419" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E419" s="3" t="n">
-        <v>-1</v>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>0</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="D431" s="2" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="E431" s="2" t="n">
         <v>0</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>0</v>
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D434" s="2" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="E434" s="2" t="n">
         <v>0</v>
@@ -10035,38 +10035,38 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D435" s="2" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E435" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="inlineStr">
+      <c r="A436" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B436" s="2" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C436" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D436" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E436" s="2" t="n">
-        <v>0</v>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C436" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="D436" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E436" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -10077,17 +10077,17 @@
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C437" s="4" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="D437" s="4" t="n">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="E437" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10859,13 +10859,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11966,27 +11966,27 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•济南华山环宇城</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>山东省济南市历城区将军路1688号华山环宇城1楼</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11998,27 +11998,27 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都五龙山</t>
+          <t>华为智能生活馆•淄博万象汇</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>淄博市</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>成都市新都区三河街道五龙山路127号</t>
+          <t>山东省淄博市张店区金晶大道66号万象汇一楼2号门入口处</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「鸿蒙智行授权用户中心•成都五龙山」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12030,27 +12030,27 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>晋城市</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>山西省晋城市城区钟家庄街道白水东街文峰路8号</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12062,22 +12062,22 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•济南华山环宇城</t>
+          <t>鸿蒙智行尚界用户中心•常州金坛汽车城</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>山东省济南市历城区将军路1688号华山环宇城1楼</t>
+          <t>江苏省常州市金坛区金坛汽车城9号</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12094,22 +12094,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•淄博万象汇</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>淄博市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>山东省淄博市张店区金晶大道66号万象汇一楼2号门入口处</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12126,22 +12126,22 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>抚州市</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>江西省抚州市临川区万达广场1036号</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -12158,27 +12158,27 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•菏泽定陶小镇</t>
+          <t>华为授权体验店（嘉善银泰城）</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>菏泽市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇迎旭路与曙光路交叉口北200米</t>
+          <t>浙江省嘉兴市嘉善县罗星街道银泰百货399号1楼华为店L1-102-2</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12190,27 +12190,27 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•中山江陵西路</t>
+          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>中山市</t>
+          <t>宁波市</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>广东省中山市火炬开发区江陵西路36号之三</t>
+          <t>浙江省宁波市鄞州区下应北路800号</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「AITO授权用户中心•中山江陵西路」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12222,27 +12222,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•惠州金山汽车城</t>
+          <t>鸿蒙智行尚界用户中心•武汉汉口北大道</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>惠州市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城D1号展场</t>
+          <t>湖北省武汉市黄陂区滠口街道滠口村刘店村汉口北汽车大世界W1号H-2#A号-1</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•常州金坛汽车城</t>
+          <t>鸿蒙智行尚界用户中心•福州华侨汽车产业园</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>江苏省常州市金坛区金坛汽车城9号</t>
+          <t>福建省福州市仓山区盖山镇齐安路767号7号楼3单元</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -12286,27 +12286,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•无锡先锋中路</t>
+          <t>AITO授权用户中心•六盘水通源</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>六盘水市</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区安镇街道先锋中路25-4号</t>
+          <t>贵州省六盘水市钟山区德坞街道钟山西路白鹤高架桥北侧通源汽车文化广场</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>连续在档 1 期；本期存在高相似店名「鸿蒙智行授权用户中心•无锡先锋中路」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12318,22 +12318,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,27 +12350,27 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>抚州市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>江西省抚州市临川区万达广场1036号</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12382,22 +12382,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（嘉善银泰城）</t>
+          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>黔南布依族苗族自治州</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市嘉善县罗星街道银泰百货399号1楼华为店L1-102-2</t>
+          <t>贵州省黔南布依族苗族自治州都匀市茂盛汽车城通源汽车文化广场</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -12414,27 +12414,27 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•宁波下应</t>
+          <t>华为授权体验店（甘井子万达）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>大连市</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省宁波市鄞州区下应北路800号</t>
+          <t>辽宁省大连市甘井子区虹韵路6号万达广场1A层1A51号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 2 期；本期存在高相似店名「鸿蒙智行授权用户中心•宁波下应」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12446,27 +12446,27 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宁波下应北路</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>西宁市</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省宁波市鄞州区下应北路800号</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12478,27 +12478,27 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•杭州梦马汽车小镇</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>西宁市</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼1层03号</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12510,377 +12510,25 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•武汉汉口北大道</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>西宁市</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市黄陂区滠口街道滠口村刘店村汉口北汽车大世界W1号H-2#A号-1</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•怀化国际汽车城</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>怀化市</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>湖南省怀化市鹤城区城南街道怀化国际汽车城内原丰田4S店</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期；本期存在高相似店名「鸿蒙智行授权用户中心•怀化国际汽车城」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•福州华侨汽车产业园</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>福州市</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>福建省福州市仓山区盖山镇齐安路767号7号楼3单元</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>华为授权体验店（甘井子万达）</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>大连市</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>辽宁省大连市甘井子区虹韵路6号万达广场1A层1A51号</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•沈阳创新二路</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>沈阳市</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>辽宁省沈阳市浑南区创新二路37-1号</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 2 期；本期存在高相似店名「鸿蒙智行尚界用户中心•沈阳创新二路」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•延安宝塔汽车园</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>延安市</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>陕西省延安市宝塔区李渠镇杨兴庄汽车城4号</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期；本期存在高相似店名「AITO授权用户中心•延安宝塔汽车园」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>西宁市</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•西宁同安路</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>西宁市</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>青海省西宁市城中区南川工业园区同安路182号</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期；本期存在高相似店名「鸿蒙智行授权用户中心•西宁同安路」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>西宁市</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 5 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>西宁市</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>连续在档 5 期</t>
         </is>
@@ -12897,7 +12545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12948,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12968,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13000,29 +12648,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13032,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米 → 湖南省邵阳市双清区邵阳大道东联接线交叉口天娇汽配城内东100米</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13064,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼 → 广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13096,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13108,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13128,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13140,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13160,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•南阳张衡大道</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13192,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角 112 号 → 河南省南阳市高新区百里奚街道北京大道与张衡西路交汇处东南角112号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13204,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•儋州新能源汽车广场</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13224,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省儋州市那大镇宝岛路99号儋州新能源汽车广场6-7号 → 海南省儋州市那大镇宝岛路99号儋州新能源汽车广场A区6号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13256,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13268,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13288,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13320,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13352,14 +13000,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼 → 内蒙古自治区鄂尔多斯市东胜区铜川镇汽贸街和兴汽车城</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13369,12 +13017,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13384,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13416,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13448,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•驻马店开源大道</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13480,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东200米路南02号 → 河南省驻马店市驿城区开源大道与兴业大道交叉口车管所北门向东 200 米路南 02号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•兴义木贾汽车园</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13512,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>贵州省黔西南布依族苗族自治州兴义市木贾汽车园 → 贵州省黔西南布依族苗族自治州兴义市木贾物流园</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13524,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13544,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鞍山建设大道</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13576,29 +13224,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>辽宁省鞍山市铁西区西环路98号 → 辽宁省鞍山市千山区西环路96号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13608,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西边南路与鞋城一路交汇处东南角 → 安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13620,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13640,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13672,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13704,39 +13352,39 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口 → 安徽省芜湖市经开区九华北路与华山路交叉口</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13748,49 +13396,49 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•沭阳常州路</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13800,7 +13448,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市沭阳县常州路19号 → 江苏省宿迁市沭阳县河东路21号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -13812,17 +13460,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13832,29 +13480,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13864,29 +13512,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13896,29 +13544,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•靖江国际汽车城</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13928,29 +13576,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>江苏省泰州市靖江市中洲西路国际汽贸城130号 → 江苏省泰州市靖江市中洲西路国际汽车城130号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13960,29 +13608,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>沈阳铁西万象汇城市展厅一号门</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>沈阳铁西万象汇体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13992,39 +13640,39 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>地址相似度 63%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -14036,921 +13684,25 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>吉林省长春市朝阳区硅谷大街5555号 → 吉林省长春市高新区硅谷大街5555号</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>宾利</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>宾利北京 - 三里屯</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>宾利北京 - 三里屯</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>广东省广州市天河区广汕一路6号101房 → 广东省广州市天河区广汕一路6号103房</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•中山江陵西路</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>广东省中山市火炬高技术产业开发区江陵西路20号之二 → 广东省中山市中山港街道火炬开发区江陵西路20号之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•郑州西四环</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>河南省郑州市高新区西四环路西冬青西街南(冬青西街91号) → 河南省郑州市高新区西四环路西冬青西街南（冬青西街91号）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•黄冈南湖路</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>湖北省黄冈市黄州区南湖路特1号 → 湖北省黄冈市黄州区南湖路93号</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•遵义黔北国际汽车博览城</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>贵州省遵义市播州区龙坑街道黔北国际汽车博览城13.14号 → 贵州省遵义市播州区龙坑街道黔北国际汽车博览城13-14号</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>云南省曲靖市经开区学府路172号 → 云南省曲靖市麒麟区学府路172号</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•大连香周路</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>辽宁省大连市西岗区香周路103号1层-3 → 辽宁省大连市西岗区香周路103号1层3号</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>陕西省西安市未央区凤城七路陕西省物流集团内 → 陕西省西安市未央区凤城七路陕西商储物流园内</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>吉林省长春市绿园区景阳大路3862号 → 吉林省长春市汽开区景阳大路3862号</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>宾利</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>宾利北京亦庄</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>宾利北京五棵松（新）</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•都匀通源汽车文化广场</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•都匀茂盛汽车城</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>宾利</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>宾利北京亦庄</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>宾利北京五棵松（新）</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>上海松江万达</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>上海松江万达广场</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>深圳光明蓝鲸世界体验店</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•六盘水通源</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•六盘水钟山</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>沈阳铁西万象汇城市展厅一号门</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>沈阳铁西万象汇体验店</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•晋城文峰路</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（相城龙湖）</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>店名相似度 96%</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>-15</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8509</v>
+        <v>8508</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8480</v>
+        <v>8479</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-29</v>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0</v>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,14 +13192,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,29 +13416,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,14 +13128,14 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,29 +13416,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13145,12 +13145,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13199,22 +13199,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,14 +13256,14 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -13273,12 +13273,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -13524,17 +13524,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12655,22 +12655,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,14 +12872,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13263,22 +13263,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（22家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安芙蓉新天地销售中心</t>
+          <t>小鹏汽车西安王府井销售中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
+          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车西安王府井销售中心</t>
+          <t>小鹏汽车西安芙蓉新天地销售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区未央路170号熙地港负一层王府井新能源展厅</t>
+          <t>西安市曲江新区芙蓉南路芙蓉新天地购物中心1F-F1005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
+          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12729,12 +12729,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,7 +13583,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -12601,12 +12601,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -13103,22 +13103,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁城东吾悦</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁城东吾悦</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城东区八一路与民和路交叉口东南西宁城东吾悦广场</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -12633,12 +12633,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,14 +13032,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13199,22 +13199,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为授权体验店（融创广场）</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号龙湖天街一层A1F-25、26号</t>
+          <t xml:space="preserve"> 江苏省淮安市清江浦区天津路融创广场一楼华为</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
+          <t>AITO授权用户中心•贵阳通源云岩</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
+          <t>贵州省贵阳市云岩区新添大道南段485号</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳通源云岩</t>
+          <t>AITO授权用户中心•贵阳观山湖通源汽车文化广场</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区新添大道南段485号</t>
+          <t>贵州省贵阳市观山湖区林城西路通源汽车文化广场一号钻石厅1楼</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁王府井百货</t>
+          <t>华为智能生活馆•西宁海湖万达</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城中区西大街王府井百货B馆</t>
+          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•西宁海湖万达</t>
+          <t>华为智能生活馆•西宁王府井百货</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>青海省西宁市城西区海湖新区西关大街海湖万达广场2号门左侧</t>
+          <t>青海省西宁市城中区西大街王府井百货B馆</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
@@ -12633,12 +12633,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,14 +12712,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州龙溪大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车广州龙溪大道销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>广东省广州市荔湾区龙溪大道488号场内自编号为86号 → 广东省广州市荔湾区龙溪大道488号金马汽车交易城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -13423,7 +13423,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>深圳光明蓝鲸世界体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店L1-07/08</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>深圳光明蓝鲸世界体验店</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创广场）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260601_vs_20260608.xlsx
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
+          <t>小鹏汽车武汉江夏永旺销售中心</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
+          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉江夏永旺销售中心</t>
+          <t>小鹏汽车武汉江宸龙湖天街销售中心</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>湖北省武汉市江夏区文化大道199号永旺梦乐城1F-1062-2</t>
+          <t>湖北省武汉市江汉区青年路518号江宸龙湖天街负一楼小鹏汽车体验中心</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期；本期存在高相似店名「小鹏汽车武汉经开永旺销售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12591,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>昆明经开特斯拉中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
+          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳福保销售服务中心</t>
+          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
+          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101317 → 新东路幸福二村40号楼 朝阳区 100027</t>
+          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米 → 湖南省长沙市岳麓区桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>河北省张家口市经济技术开发区张宣公路西侧白云街1号 → 河北省张家口市经济技术开发区白云街1号万国汽配城后</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车天津北辰双江道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
+          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上海德辰汽车销售有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
+          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
+          <t>广州市锦龙汽车发展有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
+          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐山天牛汽车城销售服务中心</t>
+          <t>小鹏汽车合肥包河汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省乐山市市中区龙游路北段518号 → 四川省乐山市市中区龙游路北段518号1幢</t>
+          <t>繁华大道29华天大厦向东20米3号整栋标准厂房 → 安徽省合肥市包河经济开发区繁华大道29华天大厦向东20米3号整栋标准厂房</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京五方天雅销售服务中心</t>
+          <t>小鹏汽车福州海盛汽车城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
+          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆万象城销售中心</t>
+          <t>小鹏汽车北京五方天雅销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
+          <t>北京市朝阳区王四营乡五方天雅B区B1-03 → 北京市朝阳区五方桥西南侧五方天雅市场内B区B1-03号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州海盛汽车城交付中心</t>
+          <t>小鹏汽车重庆万象城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福州市闽侯县荆溪镇永丰村洪甘路189号海盛汽车城 → 荆溪镇永丰村杜坞42号海盛汽车城A区5栋1层小鹏福州海盛交付中心</t>
+          <t>重庆市九龙坡区万象城北区 → 重庆市九龙坡区万象城北区3号门NL132</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>华为授权体验店（东吴银泰）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区汕汾路与淮河路交界处北侧 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车文山国际汽车城销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车文山国际汽车城销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>云南省文山壮族苗族自治州文山市腾龙北路世纪名苑二期 → 云南省文山壮族苗族自治州文山市腾龙北路世纪名苑B期第28-31号商铺</t>
+          <t>四川省遂宁市遂宁高新区物流港物流大道858-888号 → 四川省遂宁市遂宁高新区物流港主干道B南侧858-888号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>昆明经开特斯拉中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>云南省昆明市自由贸易试验区昆明片区经开区出口加工区A6-1-2号（宝泽路41号）2栋 → 云南省昆明市经济开发区宝泽路41号2栋</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东吴银泰）</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市吴兴区劳动路518号湖州东吴银泰城1F层【1001-A,1001-B,1002、1-39】号 → 湖州市吴兴区劳动路518号湖州东吴银泰城1F层C馆（1001-A,1001-B,1002-C) 华为授权体验店</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津北辰双江道销售服务中心</t>
+          <t>小鹏汽车深圳福保销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区双街镇庞大汽贸园原五菱宝骏店展厅 → 天津市北辰区双街镇庞大汽贸园原五菱骏宝店展厅</t>
+          <t>深圳市福田保税区蓝花道6号诚联物流大厦1层 → 广东省深圳市福田区蓝花道6号城联物流大厦一层</t>
         </is>
       </c>
     </row>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -13295,22 +13295,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海德辰汽车销售有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇醒群社村工业区5号 → 广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号</t>
+          <t>上海市闵行区颛兴东路1280弄3号(都会路口) → 上海市闵行区莲花南路2333号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>广州市锦龙汽车发展有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广东省广州市天河区黄村街道奥体路55号(奥林匹克体育中心东门对面) → 广东省广州市天河区奥体南路5号</t>
+          <t>海南省海口市龙华区南海大道115号福德汽车城小鹏汽车 → 海南省海口市龙华区南海大道115号</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车常州金坛汽车城销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心 → 小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车常州金坛汽车城销售中心 → 小鹏汽车常州金坛汽车城销售展厅</t>
         </is>
       </c>
     </row>
@@ -13455,22 +13455,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南新天地</t>
+          <t>上海松江万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•佛山岭南天地</t>
+          <t>上海松江万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>华为智能生活馆•佛山岭南新天地</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>华为智能生活馆•佛山岭南天地</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13519,22 +13519,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海松江万达广场</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13551,22 +13551,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达广场销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海临港万达销售展厅</t>
+          <t>宾利北京五棵松（新）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13583,22 +13583,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海临港万达广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>宾利北京五棵松（新）</t>
+          <t>小鹏汽车上海临港万达销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰</t>
+          <t>华为授权体验店（相城龙湖）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
+          <t>华为授权体验店（永旺梦乐城）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 96%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（相城龙湖）</t>
+          <t>华为智能生活馆•蚌埠银泰</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（永旺梦乐城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 96%</t>
         </is>
       </c>
     </row>
